--- a/src/attributions/attributions_ig_traj_125.xlsx
+++ b/src/attributions/attributions_ig_traj_125.xlsx
@@ -2137,25 +2137,25 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01788723902997303</v>
+        <v>0.01557053249925868</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.006169121784241308</v>
+        <v>0.004181604586750498</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.002978984062430998</v>
+        <v>-0.005101176965814505</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003630472437013819</v>
+        <v>0.03355430274264521</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,25 +2176,25 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01352316813380628</v>
+        <v>0.007578523191690591</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01292427561445731</v>
+        <v>-0.01821284049761528</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0002748582623588493</v>
+        <v>0.01065272171629928</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.006198934832838443</v>
+        <v>0.02686464037334138</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01267333769764911</v>
+        <v>0.01177955557678754</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
@@ -2215,31 +2215,31 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0209208255987431</v>
+        <v>-0.02948719727724371</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02286361699571059</v>
+        <v>-0.01479706515470629</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.006667677357716609</v>
+        <v>-0.0232349911933462</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.005186733565645832</v>
+        <v>0.002480981341937295</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01038175631493995</v>
+        <v>-0.01470928130531478</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.002389904053734298</v>
+        <v>-0.006824073671975885</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2275,88 +2275,88 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.06045263325550686</v>
+        <v>0.1154142929635504</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.03360753664806899</v>
+        <v>-0.006852118532171484</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.01193455352780415</v>
+        <v>-0.01553441752658047</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.009947257794962187</v>
+        <v>-0.01244924865203433</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02093804795223217</v>
+        <v>-0.01171567643627712</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.008073516910160413</v>
+        <v>-0.02014073808599712</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.01774092850165324</v>
+        <v>0.01413734629769327</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.007611485329593208</v>
+        <v>0.03978252371654848</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01350781914656308</v>
+        <v>0.0301382364520922</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.00209108274419189</v>
+        <v>-0.002048149389814083</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0009572859281914302</v>
+        <v>0.00219622840507542</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.001265539763789571</v>
+        <v>0.003190763009644357</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
@@ -2380,49 +2380,49 @@
         <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.0005145078100425605</v>
+        <v>-0.01335032686188702</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001452768320459161</v>
+        <v>-0.006296930736390562</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01792948873526958</v>
+        <v>0.02469162150289591</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.009649936602061118</v>
+        <v>-0.02045312359927019</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01139754829601182</v>
+        <v>0.02865791775302746</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.007546743885256045</v>
+        <v>0.01377816698421063</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2431,52 +2431,52 @@
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.001721372067149207</v>
+        <v>-0.01644186848930821</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001009354351061101</v>
+        <v>-0.007661973523163966</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01784478181369086</v>
+        <v>0.02218155856160344</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.002938868052064987</v>
+        <v>-0.007706144936372702</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0001920435964206871</v>
+        <v>-0.01786897814731767</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.02093545957287496</v>
+        <v>0.002213281060547496</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,106 +2485,106 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.008214485741631807</v>
+        <v>-0.006037375754436114</v>
       </c>
       <c r="DP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.003815660944152529</v>
+        <v>0.01394373929799205</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.005803944290699419</v>
+        <v>0.0410113214661251</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.004985218461379053</v>
+        <v>0.002232418585309736</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02817009290726326</v>
+        <v>0.01014049208007134</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.003785772134975926</v>
+        <v>-0.02225763409303548</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0002413310325629412</v>
+        <v>-0.02892949132791499</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.003026317546645401</v>
+        <v>-0.01983890786790573</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.003710890212110911</v>
+        <v>0.003923709214634376</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.004476559560080078</v>
+        <v>0.007796717009947673</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.001753694598090696</v>
+        <v>0.003440591055286926</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.02924783744314201</v>
+        <v>0.02113060811693268</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.0005419476673011349</v>
+        <v>-0.01809340052734349</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.000917442497608016</v>
+        <v>-0.01406692102482895</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.01498212409512559</v>
+        <v>0.02101037524453927</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.02646171211809471</v>
+        <v>-0.02317110686861649</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.03096952380882109</v>
+        <v>-0.001597922923166025</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.007299307705780051</v>
+        <v>-0.01245824258187884</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.002046403238640995</v>
+        <v>0.002050475742135625</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.002118571738029112</v>
+        <v>0.003501146905080376</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03132740433775768</v>
+        <v>0.02350469224407713</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,25 +2674,25 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
         <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02060904232583149</v>
+        <v>0.000540494380115287</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.007410550652823883</v>
+        <v>0.02127149425743811</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1538185957137352</v>
+        <v>0.05255537631910977</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1050011255484465</v>
+        <v>-0.05912955743888279</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01467962087238325</v>
+        <v>-0.01195885712028288</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2733,25 +2733,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1286377118150642</v>
+        <v>0.0581583769436854</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0832849856058029</v>
+        <v>-0.06635176538841361</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02846439739632293</v>
+        <v>-0.007258248763776749</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2763,19 +2763,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01128887624312271</v>
+        <v>0.004227006445384578</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001840467661366441</v>
+        <v>0.01063526310410403</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01543289675809992</v>
+        <v>0.02343109724930837</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,19 +2787,19 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.08636609653298045</v>
+        <v>-0.005392392034286615</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.06010035396492631</v>
+        <v>-0.001372201722963171</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.08651960379291961</v>
+        <v>-0.01751370794035215</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01353271686599195</v>
+        <v>0.02140221771175805</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.04007864360913247</v>
+        <v>-0.0473589371357892</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.02602217962651453</v>
+        <v>0.003095060265142576</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.406543069491958</v>
+        <v>0.1492714390038806</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.0351686836676873</v>
+        <v>-0.1054698601576357</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1696309329888061</v>
+        <v>-0.03642748652839107</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,28 +2865,28 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.004829113015839249</v>
+        <v>0.001243688632638182</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.07246986014742123</v>
+        <v>-0.01542202214993127</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.07553745412617004</v>
+        <v>-0.01335921239038508</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
@@ -2898,22 +2898,22 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01249798299397514</v>
+        <v>-0.01023659172852867</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.08369901284946767</v>
+        <v>-0.00329010361001621</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.08335128668018017</v>
+        <v>0.08384447332283036</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,22 +2925,22 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.01727843851762532</v>
+        <v>-0.00471955832455497</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.05304600638683674</v>
+        <v>0.06052801580475176</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001701330021203633</v>
+        <v>0.003635753864964198</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2949,82 +2949,82 @@
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.09551175427613884</v>
+        <v>-0.05704301911873685</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02212996490190682</v>
+        <v>0.03544168022213851</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.03216773308368684</v>
+        <v>0.02300945350441931</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.03857860998949223</v>
+        <v>-0.04277033619921236</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0712492544802206</v>
+        <v>0.05777584331559823</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1243582290465805</v>
+        <v>0.03298020465836723</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.09895174116957269</v>
+        <v>-0.06046018265291336</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.04257156509197368</v>
+        <v>0.04066162316691904</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01097725882610638</v>
+        <v>0.01871819656859606</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,79 +3033,79 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004557416099069247</v>
+        <v>-0.002152692628090744</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.04394079308824615</v>
+        <v>0.007317956168061608</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.03124697574204882</v>
+        <v>-0.005497831587967224</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1409075065101117</v>
+        <v>-0.01888830226334303</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01465874138277226</v>
+        <v>0.004948987602403259</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.02903231411736519</v>
+        <v>-0.02512328590656905</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.003954088624971069</v>
+        <v>0.01886854454630243</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.02456483450152074</v>
+        <v>0.06762635046840668</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.08949041112084641</v>
+        <v>0.006496608645408436</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,25 +3114,25 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0326765871195539</v>
+        <v>-0.05385231065271655</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.005523853980974637</v>
+        <v>0.01620460289784977</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.057095377614889</v>
+        <v>0.01534030779389389</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1020772060268785</v>
+        <v>-0.01815738207340135</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.06125149623905828</v>
+        <v>0.02786327545657028</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02415800275830667</v>
+        <v>0.02405206362565581</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3168,46 +3168,46 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1025180198333769</v>
+        <v>-0.06774733634814335</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.05340218931383708</v>
+        <v>0.03819022243242078</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02198299841547213</v>
+        <v>0.01525062975029051</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.008357542288410607</v>
+        <v>-0.04899363568278978</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.07463878145602466</v>
+        <v>0.02956852548191957</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.05256382144655315</v>
+        <v>0.04761710137731733</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3219,19 +3219,19 @@
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.004875069940460814</v>
+        <v>0.0387061436211936</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.1114052808010818</v>
+        <v>0.1527288637779596</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.1518854579331587</v>
+        <v>-0.0247851275640242</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
@@ -3243,19 +3243,19 @@
         <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.0228905829770002</v>
+        <v>-0.05670869925343882</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.01546890827586173</v>
+        <v>-0.01256385276977901</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
@@ -3267,10 +3267,10 @@
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01732843427520229</v>
+        <v>0.01888081070982896</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.000757920388540742</v>
+        <v>0.007196363241982673</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004071941065468733</v>
+        <v>0.007318005451909445</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007672137452666446</v>
+        <v>0.03848911705008632</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,16 +3314,16 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.00563272138839092</v>
+        <v>0.002658815764644424</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.004174024454726813</v>
+        <v>-0.005772035106298769</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000286606180640165</v>
+        <v>0.0009199149797451466</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002479823097700543</v>
+        <v>0.005086540219144436</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.007610729710548746</v>
+        <v>0.0008674377470689682</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02304692311855344</v>
+        <v>-0.03011349069211634</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01523340913467962</v>
+        <v>-0.02897178121689171</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001038349171224043</v>
+        <v>-0.01313511847125556</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.003358593648470517</v>
+        <v>0.002850912064362296</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,25 +3395,25 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.005900060119722279</v>
+        <v>-0.002841400594169213</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.002659833459636625</v>
+        <v>-0.008337890797549739</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.05094491766521728</v>
+        <v>0.08395666062194371</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0004194999484507875</v>
+        <v>-0.01211350655189087</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.009317865059185304</v>
+        <v>-0.01624719958447091</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3434,28 +3434,28 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.002861049383754303</v>
+        <v>-0.00946511600330553</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01929819231770547</v>
+        <v>-0.008209754089382655</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.002224835889380155</v>
+        <v>-0.008265100062983076</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.008526222787695282</v>
+        <v>0.01463560649129104</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.006461823528922876</v>
+        <v>0.03427871871979631</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.007632961109049933</v>
+        <v>0.02014557576634753</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001421422930367228</v>
+        <v>-0.002794487854982955</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.000213883842035704</v>
+        <v>0.0004928072457030212</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0006641280946216713</v>
+        <v>0.002201869837398654</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001934318317750004</v>
+        <v>-0.008741814758980931</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.004485601893566461</v>
+        <v>-0.005254574974342826</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.008940074585245754</v>
+        <v>0.02021370711790595</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3545,76 +3545,76 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.004831832155681555</v>
+        <v>-0.01543855817763871</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0007261644518541469</v>
+        <v>0.02286899359945722</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01170073511052333</v>
+        <v>0.01502324519341075</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.0002495887592654431</v>
+        <v>-0.01084972266314349</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.005998957039111883</v>
+        <v>-0.003699791454961344</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01111249376724796</v>
+        <v>0.01723566888112109</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.009988183848969275</v>
+        <v>-0.01086324624611755</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-3.608229212111343e-05</v>
+        <v>-0.001099616047219558</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0290436317518898</v>
+        <v>0.005958803343776478</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0104031821198211</v>
+        <v>-0.007190757236175752</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.002540468477630783</v>
+        <v>0.006282145798579834</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.002784859491512921</v>
+        <v>0.03070043683664156</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,61 +3656,61 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01290459634901565</v>
+        <v>-0.01033467068863096</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01112448899213213</v>
+        <v>0.0129212227877227</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.00701407117867173</v>
+        <v>0.01688314667614554</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0004911411216414659</v>
+        <v>-0.01590028085399426</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.002193232393899534</v>
+        <v>-0.0115140748609161</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.001234813318825483</v>
+        <v>0.002893599234491215</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.00926440811053658</v>
+        <v>0.002836945129913523</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
@@ -3719,10 +3719,10 @@
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01151669232774646</v>
+        <v>-0.007048719023966539</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03063635838093927</v>
+        <v>0.0147912761883998</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.002029908308333528</v>
+        <v>-0.01367882104263653</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,37 +3746,37 @@
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.006445361012277704</v>
+        <v>-0.01107033638273193</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.009034130338291719</v>
+        <v>0.01592921946391293</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01794697158346966</v>
+        <v>-0.02261736177972295</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01711638280821613</v>
+        <v>0.01509945872483823</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01706512299865501</v>
+        <v>0.004540379443670086</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,25 +3785,25 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.002822424336661034</v>
+        <v>0.003969293090677698</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.009646776030075951</v>
+        <v>0.009723260935278066</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.01018819783552861</v>
+        <v>-0.007831989210154182</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,34 +3812,34 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01593715009714854</v>
+        <v>0.001407913487288362</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.005238336270298332</v>
+        <v>0.01583604248722931</v>
       </c>
       <c r="GE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF6" t="n">
         <v>0</v>
       </c>
       <c r="GG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07964658366624791</v>
+        <v>0.02545818068282818</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0124273327847282</v>
+        <v>-0.003117566689310355</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02657453487153946</v>
+        <v>0.003678299036062912</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04256233047078197</v>
+        <v>0.04383419201219855</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06226948799710332</v>
+        <v>-0.008185579045047933</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.01020600981627819</v>
+        <v>-0.0001165901297758794</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.847666464103345e-11</v>
+        <v>-1.836696725359376e-12</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,52 +3910,52 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005295661736090916</v>
+        <v>0.003803764194986842</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001625467518021707</v>
+        <v>0.001589664370058557</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06303970923986613</v>
+        <v>-0.0217039186810134</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03251679324152879</v>
+        <v>-0.006060349952000429</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.02092012044698214</v>
+        <v>0.001729601854400709</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02720623178904479</v>
+        <v>0.01198157183926905</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01673075342276328</v>
+        <v>0.0008580571202279617</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01124574841084781</v>
+        <v>-0.004849623725396604</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2359566862331668</v>
+        <v>0.09903206680703136</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1198315920469325</v>
+        <v>-0.009712143975366877</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,67 +4003,67 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.009296248885170633</v>
+        <v>0.006576993881464116</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.04252459183814412</v>
+        <v>-0.01540814350364663</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.09152398232596817</v>
+        <v>-0.007873788845560033</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0190185228641242</v>
+        <v>-0.005035801919873492</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0266155549661026</v>
+        <v>0.002773033607924171</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.09505670796783107</v>
+        <v>0.0299632098865662</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02193903733334758</v>
+        <v>0.009136506027489132</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.008702793644363658</v>
+        <v>-0.003334993988491855</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,25 +4072,25 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0003963738745629511</v>
+        <v>0.001335191073218173</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.001923080011109709</v>
+        <v>0.0008215839037669367</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.03009904337979843</v>
+        <v>-0.01860037268602404</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002716378941785376</v>
+        <v>0.001657687053195838</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,40 +4111,40 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.04228173860253838</v>
+        <v>0.009675360197060794</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.002679439123593939</v>
+        <v>-0.02587481595615875</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0285001438069166</v>
+        <v>0.005874518658761605</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.005651396438704645</v>
+        <v>0.02387302233299164</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.03801755873883503</v>
+        <v>-0.01906961806499466</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.008906788289796177</v>
+        <v>0.003019171732661744</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4165,22 +4165,22 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03219267558086653</v>
+        <v>0.008676791507096505</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.06181879291990163</v>
+        <v>-0.009225946330318395</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05678398419514651</v>
+        <v>-0.00235226735445993</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,124 +4189,124 @@
         <v>-0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.01261907793519688</v>
+        <v>-0.01356939701610042</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.01528506469456528</v>
+        <v>-0.005979962677093442</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.0183879733540554</v>
+        <v>0.009131538271850936</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.03122160210479629</v>
+        <v>-0.01073415396740241</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.02254913815372336</v>
+        <v>0.001088985351719224</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01592832988219669</v>
+        <v>0.001099557813440364</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.00911386164399104</v>
+        <v>0.006619627611655172</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.01244425463861165</v>
+        <v>-0.02575805163531331</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02929353826320031</v>
+        <v>-0.001083424003063669</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.04520033897594729</v>
+        <v>0.009382938657596106</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.06587178857250213</v>
+        <v>-0.00668179514024814</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.002041300595869191</v>
+        <v>0.009829825908661806</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0424174005328991</v>
+        <v>0.004651452969938355</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04822507643014418</v>
+        <v>-0.02296349680790439</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.002807764493339367</v>
+        <v>-0.002605815834432534</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02127972341431316</v>
+        <v>0.009278074335904433</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.06768998722372521</v>
+        <v>-0.01657289418870099</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.01010588620122697</v>
+        <v>-0.005961674769770184</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,25 +4351,25 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.04108697310218059</v>
+        <v>0.02976845016380562</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.06056574820765532</v>
+        <v>0.01301797042143501</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.06381828727444162</v>
+        <v>-0.000728467651808092</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4381,13 +4381,13 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.005619058650449769</v>
+        <v>-0.0002740994653172704</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.06213682323298531</v>
+        <v>-0.003246319694072351</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03194033294828286</v>
+        <v>-0.003339843705065014</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3179221134606067</v>
+        <v>0.08461020255620452</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1647397239222605</v>
+        <v>-0.08273971636358635</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0595692770413598</v>
+        <v>0.001451887952252651</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,19 +5012,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2572367777062727</v>
+        <v>0.1002150564625409</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1847745025729399</v>
+        <v>-0.115643771691641</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09464455763205641</v>
+        <v>0.001328231551222294</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5039,25 +5039,25 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01638068379019082</v>
+        <v>0.001270076285137188</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.223594695455653e-11</v>
+        <v>-2.651057077902808e-11</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01043891497183176</v>
+        <v>-0.008168757752638296</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1451441359719224</v>
+        <v>0.01032251012032126</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.04805400765630993</v>
+        <v>-0.0128529123090905</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.02427107656672078</v>
+        <v>-0.01029660796005069</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.03761110849855581</v>
+        <v>0.03475650471077459</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03300857834951033</v>
+        <v>-0.05161454503712827</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.05391954012002573</v>
+        <v>0.008123493189364932</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5117,22 +5117,22 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.5584485728657187</v>
+        <v>0.1408463135027109</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.01689904771910553</v>
+        <v>-0.0808262194318629</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1356717201953516</v>
+        <v>-0.06263359669126281</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,22 +5141,22 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0108298726392769</v>
+        <v>0.003411052455120292</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.09428984705304636</v>
+        <v>-0.00283896641863126</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.2097187707363352</v>
+        <v>0.005277417233252152</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.06334375758834193</v>
+        <v>0.007530617690520955</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.07659713391347985</v>
+        <v>0.006644120125050761</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.07890440611278826</v>
+        <v>0.05428754529530883</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.02005213959517693</v>
+        <v>-0.007594231943908398</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0592424907570702</v>
+        <v>0.0888200306912986</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003175364861980009</v>
+        <v>0.002925276265136516</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1225295331790329</v>
+        <v>-0.05988446633380536</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.02356995549767228</v>
+        <v>0.07576776062207642</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01583684327240147</v>
+        <v>0.005898792229365525</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
         <v>-0</v>
@@ -5249,25 +5249,25 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.03806822100987543</v>
+        <v>-0.07072624829842486</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1751476477340577</v>
+        <v>0.1331688949589465</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1181983978306827</v>
+        <v>0.0231409356624607</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,55 +5276,55 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.107862897263174</v>
+        <v>-0.05449303802939414</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.04935937399088182</v>
+        <v>0.07650176402492778</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001690478057737165</v>
+        <v>0.006415366631700298</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.009951681529745295</v>
+        <v>-0.001920530043339916</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1046995022406647</v>
+        <v>0.01444570609146881</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02640243089546615</v>
+        <v>-0.03809165434428451</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,22 +5336,22 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.09986260652010957</v>
+        <v>-0.05690162054938265</v>
       </c>
       <c r="DP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.02691857499223795</v>
+        <v>0.05524163273883981</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.03073320795544547</v>
+        <v>-0.003433426392411188</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,49 +5363,49 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.04571776212190443</v>
+        <v>-0.009144339473773161</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.01186040387570168</v>
+        <v>0.05085217138020031</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.09752088134233201</v>
+        <v>-0.002134528818478493</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.05445276304106714</v>
+        <v>-0.02518829530158292</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.01264948451259812</v>
+        <v>0.04684817591100408</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.02937147571000291</v>
+        <v>0.02162660990145509</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5417,22 +5417,22 @@
         <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.0867542033432826</v>
+        <v>-0.04823219996736517</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.05305468427083998</v>
+        <v>-0.05211567835666093</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.04842663227291883</v>
+        <v>0.03709404857997092</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,70 +5444,70 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1089140830946097</v>
+        <v>-0.06509454293516796</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.03773907851197563</v>
+        <v>0.0888055147332404</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.008663868234196626</v>
+        <v>0.002759353386570708</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.07574526038615911</v>
+        <v>-0.03247449161414616</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04709458881408575</v>
+        <v>0.0009260563260045966</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.1445225861828688</v>
+        <v>-0.02830671493348763</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.06153756246954555</v>
+        <v>0.03349932225034307</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.06878030862270362</v>
+        <v>0.1009252863774738</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.2086948098341997</v>
+        <v>-0.03232665185239241</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
@@ -5522,16 +5522,16 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-5.381144749810971e-05</v>
+        <v>-0.03104639828453745</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.01817027770957336</v>
+        <v>0.01058015642232636</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,10 +5543,10 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,79 +5554,79 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3242559175999479</v>
+        <v>0.08206827458193842</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1702359215666998</v>
+        <v>-0.0363455618404058</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1289787761277523</v>
+        <v>-0.009644002711456455</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01567006202966175</v>
+        <v>0.01113794497438256</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2213088711628387</v>
+        <v>0.08862525434822341</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1620361352487222</v>
+        <v>-0.08143401594431147</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1568405561762785</v>
+        <v>-0.006486782121337281</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.006910791819385042</v>
+        <v>0.004776549779821124</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.02429481555918948</v>
+        <v>0.004480704622513559</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.017991307141953</v>
+        <v>-0.01970734470186273</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.03162556466614014</v>
+        <v>-0.03033378737509681</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.03550995888023271</v>
+        <v>0.04779468667074114</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,16 +5635,16 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.05802564371326514</v>
+        <v>-0.00869813746370135</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.05556039472056058</v>
+        <v>-0.001069034541984576</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01881612815494495</v>
+        <v>-0.1272899569651532</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.02957057597977448</v>
+        <v>0.003733029276670295</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -5662,133 +5662,133 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01389233517744302</v>
+        <v>0.03577490032888671</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.03464017450125513</v>
+        <v>-0.0215413622142326</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.05883319852901644</v>
+        <v>0.005066889211557239</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.01517287232451744</v>
+        <v>-0.01394479608405415</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2827071085281042</v>
+        <v>0.1154563600247545</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.05452564836297851</v>
+        <v>-0.01023402395080826</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.04786235290592098</v>
+        <v>-0.06473582147248376</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.1189864808885801</v>
+        <v>-0.06707411974231217</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.007000034031850705</v>
+        <v>-0.01812222173423935</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.09012694355466713</v>
+        <v>-0.009952736803659769</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2295831042164329</v>
+        <v>-0.05679209518224734</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001688505889214575</v>
+        <v>-0.0037439771411021</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1044364524707548</v>
+        <v>0.0379747694049168</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1373173489439664</v>
+        <v>0.001579720040673868</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.007584019066766386</v>
+        <v>0.03636149773750466</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.03003650372244126</v>
+        <v>0.02981404611588036</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1214429476763036</v>
+        <v>0.05449409482173459</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.006359682959073994</v>
+        <v>0.005791088172863563</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01116392230574837</v>
+        <v>0.007275184123558143</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.006019227172480189</v>
+        <v>0.005908019825439986</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5797,325 +5797,325 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.09624857967574864</v>
+        <v>-0.03587509631726124</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.03882622814843542</v>
+        <v>0.01927024031400248</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.0006424980232695485</v>
+        <v>0.008052681076772289</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.01873791472583182</v>
+        <v>0.008874643125782835</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.1070114708638078</v>
+        <v>-0.05975587081818182</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.03818366708962428</v>
+        <v>0.03152015215104465</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.03403174673437134</v>
+        <v>0.1131781218045243</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.05785791500934768</v>
+        <v>0.06554794440300603</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.08092830576970123</v>
+        <v>-0.0362434306060681</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.06813412174373706</v>
+        <v>0.02327082923667334</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.001188941667092684</v>
+        <v>0.01106005279482779</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01821326732488437</v>
+        <v>0.001352582732488952</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.1070017898552397</v>
+        <v>-0.01512288882647447</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.07589780726453228</v>
+        <v>0.00684370575222702</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01715357811718839</v>
+        <v>-0.00865133469098546</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0008886115097908421</v>
+        <v>-0.005677859184265027</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.09120689683407796</v>
+        <v>-0.02077301059119866</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.001771558784648345</v>
+        <v>0.0051773973973041</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.04387918388695911</v>
+        <v>-0.05219587974562868</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.02378363138994948</v>
+        <v>0.07432211754049876</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.04116677885661672</v>
+        <v>0.02329900783864063</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0616910918641662</v>
+        <v>0.04186358975268917</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.1033096043822433</v>
+        <v>-0.03507561485413981</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.01834514822200275</v>
+        <v>0.08293713838549817</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.01393898206693834</v>
+        <v>-0.007178659116303921</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.007291170418989234</v>
+        <v>0.003386517436870031</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03019113846167033</v>
+        <v>-0.03365292050800822</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.07024200318724699</v>
+        <v>0.01011241030939377</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1123824701268607</v>
+        <v>-0.002068516879216558</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.06826389477308842</v>
+        <v>0.01647762200724374</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.01955427320570292</v>
+        <v>0.01400756708988462</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.02519392373199158</v>
+        <v>0.02013281441503681</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0866267222628111</v>
+        <v>-0.04673136915042286</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.07429463359571289</v>
+        <v>0.0254049955907758</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01453717601659394</v>
+        <v>0.009142976934026254</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.01599471844250073</v>
+        <v>0.005904071932370411</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.03805690896911727</v>
+        <v>-0.02872942390328123</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.05128090278693257</v>
+        <v>0.008912588147937002</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.09747802404617768</v>
+        <v>0.05715065992086775</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.02171331513930543</v>
+        <v>-0.0074494405321684</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.04830345152723463</v>
+        <v>0.02253311632025995</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.004435146938366403</v>
+        <v>0.1105519993294676</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.05984147734364812</v>
+        <v>-0.08853648360193077</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.125887836242482</v>
+        <v>0.02655820072035321</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02940292558483586</v>
+        <v>-0.01878738849326422</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.005251292258420202</v>
+        <v>-0.03412818990585622</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.1117978840448396</v>
+        <v>-0.009282975377049295</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03771269863430635</v>
+        <v>0.3078381158021848</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,16 +6132,16 @@
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.07284522238079591</v>
+        <v>0.05452919159011169</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05418589992677872</v>
+        <v>-0.2803701850951138</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01962179874231533</v>
+        <v>0.3144340263734346</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,10 +6159,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.08227530595443676</v>
+        <v>-0.009042245902222282</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.04662844420246236</v>
+        <v>-0.2388738512496404</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
@@ -6174,10 +6174,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0009066779054354866</v>
+        <v>0.02010900001945695</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,52 +6186,52 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.00495406889070229</v>
+        <v>-0.05729964164203734</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00525869068361562</v>
+        <v>-0.01573134817028749</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04746175710952659</v>
+        <v>-0.02393549919640586</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.04519609450072039</v>
+        <v>-0.1991978641258486</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02351535017688422</v>
+        <v>0.08598342254967355</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.009692380743570289</v>
+        <v>0.0570268396467178</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,25 +6240,25 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.03644100452018106</v>
+        <v>-0.02913766007952938</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.008700912337727473</v>
+        <v>-0.02118990574050026</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0710829884113456</v>
+        <v>0.2898153531800252</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,43 +6267,43 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.05914620791578212</v>
+        <v>-0.1139933178460172</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.004220653466732805</v>
+        <v>-0.05921533638095006</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.007579658420612973</v>
+        <v>0.07381149137515366</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.05772306766173121</v>
+        <v>-0.0136658394026307</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.07093776927745206</v>
+        <v>-0.1674561581677253</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,34 +6312,34 @@
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.08222703940039466</v>
+        <v>0.05734648425098466</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.04746607016945629</v>
+        <v>0.1330427217088248</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.03385961794824316</v>
+        <v>0.09758002209435516</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.01154874591071053</v>
+        <v>0.1199293667119594</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.02198489875179875</v>
+        <v>-0.01734453318500529</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.004353975391699954</v>
+        <v>-0.08095868617052349</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6360,52 +6360,52 @@
         <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.00135295292502584</v>
+        <v>-0.1357853785706028</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01760180089387806</v>
+        <v>-0.03327920138729567</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02618601236303165</v>
+        <v>0.1270242062377895</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.0100028775633461</v>
+        <v>-0.135683251296854</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.01647833989939039</v>
+        <v>0.07599470490409707</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.02206817509768443</v>
+        <v>0.04032270359119623</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
@@ -6414,82 +6414,82 @@
         <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.01472388664327516</v>
+        <v>-0.1166536352910156</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>-0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01611775300005169</v>
+        <v>-0.02587647890248816</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01855003268036398</v>
+        <v>0.1308559361527845</v>
       </c>
       <c r="DB11" t="n">
         <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.01263616914422087</v>
+        <v>-0.1157093914632697</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.000641729683063632</v>
+        <v>-0.1312268389097812</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02338009931331589</v>
+        <v>0.1080459457938546</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.005519652557754151</v>
+        <v>-0.0603218861352439</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02659954212259674</v>
+        <v>-0.02218837237254393</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.00414969419517269</v>
+        <v>0.01801837222958554</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
@@ -6498,25 +6498,25 @@
         <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.00693261354146053</v>
+        <v>-0.0315783763640519</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.0342750278502947</v>
+        <v>0.008259597674628699</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01051443514758996</v>
+        <v>0.05964506854496218</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
@@ -6528,34 +6528,34 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0113418575042054</v>
+        <v>-0.08411725915575055</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.008745318381437583</v>
+        <v>-0.09079043009578364</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.00477046294942826</v>
+        <v>0.08550255008322623</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.001148188590191163</v>
+        <v>-0.05717260791326562</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
@@ -6564,25 +6564,25 @@
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.00450412311576691</v>
+        <v>-0.1103858748875844</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.02173675864639018</v>
+        <v>0.1504712101661304</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.00921735790844553</v>
+        <v>-0.1385897941118689</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,25 +6591,25 @@
         <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.02269656904057981</v>
+        <v>-0.06237786208552423</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02364786444082068</v>
+        <v>0.1113397668284117</v>
       </c>
       <c r="FD11" t="n">
         <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.005383931894720102</v>
+        <v>-0.1753654564752434</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
@@ -6618,16 +6618,16 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.04556906611552421</v>
+        <v>0.06577100577810963</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03468080071755338</v>
+        <v>0.1179106290804278</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01361601686611877</v>
+        <v>0.0786884577822759</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,28 +6645,28 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01878252735084786</v>
+        <v>0.1072711526850171</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.03851158036905351</v>
+        <v>0.06226813908123944</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.04020530860974372</v>
+        <v>-0.06153486479407054</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
@@ -6675,13 +6675,13 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.02958379918168565</v>
+        <v>0.1409710732882047</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4601476600043536</v>
+        <v>0.4334048141338472</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3474009655473532</v>
+        <v>-0.3256395976365047</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1344470930148578</v>
+        <v>-0.00906303651212842</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6716,22 +6716,22 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3027312094637791</v>
+        <v>0.4196903271832849</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3405171765351987</v>
+        <v>-0.4200283131367104</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1261301496566502</v>
+        <v>-0.04358417048015579</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
         <v>-0</v>
@@ -6743,28 +6743,28 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05733482377695589</v>
+        <v>0.04261631520019239</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02145082212079456</v>
+        <v>-0.02495260038725807</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.04625941516326223</v>
+        <v>-0.03491556490516318</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,43 +6773,43 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1675449849642255</v>
+        <v>-0.06755715227430707</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1194273091833447</v>
+        <v>-0.08125308776689663</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.04371380882731901</v>
+        <v>-0.0403534095352656</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04539076939295304</v>
+        <v>0.1192045668012763</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04069637384608842</v>
+        <v>-0.1060281728182179</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.08576122024636278</v>
+        <v>0.07361448818716965</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,25 +6818,25 @@
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4234529436562283</v>
+        <v>0.2891807365095851</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.08839968923540002</v>
+        <v>-0.2250083073406788</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.004754948956134694</v>
+        <v>-0.1255643339766009</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6848,22 +6848,22 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.003770499448439103</v>
+        <v>0.01750759184994749</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.09827722616081529</v>
+        <v>-0.02603672026279161</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.2167906577379461</v>
+        <v>-0.008941081523740003</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,58 +6872,58 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1191896629659722</v>
+        <v>-0.0837674356674153</v>
       </c>
       <c r="BN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.08000471380574327</v>
+        <v>0.03629198062454577</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.001444719173573839</v>
+        <v>0.03233628349649782</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1426814239814305</v>
+        <v>0.1557236929790793</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.0282836365704555</v>
+        <v>-0.05388528307252154</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.03970649072910744</v>
+        <v>0.003465572223102471</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
@@ -6935,46 +6935,46 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1234926895667468</v>
+        <v>-0.1964215387396233</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.02895690708351668</v>
+        <v>0.1928687837978077</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01839918528898473</v>
+        <v>-0.01291033389427243</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.03959432431050407</v>
+        <v>-0.1548056863771123</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1828643529983759</v>
+        <v>0.3164388750074141</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.0754405736143826</v>
+        <v>0.02251565328602875</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,55 +6983,55 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09265578710087979</v>
+        <v>-0.1920534269238773</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.06671341745375926</v>
+        <v>0.1849344561198511</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.0110509569861853</v>
+        <v>0.006355386543425462</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.07086346492058389</v>
+        <v>-0.108673322193772</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04553391494949899</v>
+        <v>0.03409215409577721</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1500646350241857</v>
+        <v>-0.08283559724107423</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.1202893142180306</v>
+        <v>-0.1144617071035662</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.08975071149809154</v>
+        <v>0.0675046849848689</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.06393824808641117</v>
+        <v>-0.001150704432745961</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
@@ -7070,25 +7070,25 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.007555374597517854</v>
+        <v>-0.006060818919958653</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.1053123380946859</v>
+        <v>-0.1326833909688772</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.1190998202384782</v>
+        <v>0.08485996826563814</v>
       </c>
       <c r="EB12" t="n">
         <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,163 +7097,163 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02673844180981782</v>
+        <v>-0.1433797652616856</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.04988289096710433</v>
+        <v>0.1627623959113767</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.07650924691654307</v>
+        <v>0.06077567158476545</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.08522487509787674</v>
+        <v>-0.1734566677284586</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.108078510968077</v>
+        <v>0.1312717234626803</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04949720579236996</v>
+        <v>0.03474219888608712</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.09042025104341254</v>
+        <v>-0.2072747582249833</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.07421064441895547</v>
+        <v>0.2195546968263546</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01831084133123074</v>
+        <v>-0.01835746849020219</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.004637772800570485</v>
+        <v>-0.1113366887963231</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.07682842588800803</v>
+        <v>0.05892424427127386</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.06846285729181696</v>
+        <v>-0.04255290877795491</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.04827752807670967</v>
+        <v>0.1665029095399951</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.001626282628145889</v>
+        <v>0.1906578662030601</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.214637661880917</v>
+        <v>0.1377612807791788</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01258850058064878</v>
+        <v>-0.1314536130234895</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.01563793817265138</v>
+        <v>0.1219927517501999</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.09298468702819418</v>
+        <v>0.2895959506863337</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01879208439687306</v>
+        <v>0.02674085946101529</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1545442816975313</v>
+        <v>-0.3110466141183762</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06832804343554719</v>
+        <v>0.333960010413405</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,13 +7297,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01697678724384011</v>
+        <v>-0.03893075532249766</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1463432763455178</v>
+        <v>-0.2835707627423263</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-0</v>
@@ -7312,10 +7312,10 @@
         <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.003353818085386224</v>
+        <v>0.02772164398864649</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,37 +7324,37 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.02182799887105801</v>
+        <v>-0.1165150334147659</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01359087149256468</v>
+        <v>-0.04164181766330789</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.03066847497262279</v>
+        <v>-0.1298770007939199</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.05742204272863975</v>
+        <v>-0.2107744935404972</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.007201586694408619</v>
+        <v>-0.135529983073504</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.004429772396263922</v>
+        <v>0.06989465556514995</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.006719642098228876</v>
+        <v>-0.00319463787944771</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01111134975353944</v>
+        <v>-0.06226131603035338</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7396,19 +7396,19 @@
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.06988504623829697</v>
+        <v>0.3888740739878891</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.02539268194332784</v>
+        <v>-0.1107881666839206</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.06256842803693977</v>
+        <v>-0.07908731121040791</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -7423,49 +7423,49 @@
         <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03817543014900541</v>
+        <v>-0.02318671053881849</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.02944923315156045</v>
+        <v>-0.1390089296981838</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.06600505730720493</v>
+        <v>-0.2749741827752823</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
         <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.03556074083089543</v>
+        <v>-0.004097489400028167</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03020526686991719</v>
+        <v>0.0456773869079747</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.987162675838798e-06</v>
+        <v>0.06238941356084661</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.01616488258381741</v>
+        <v>0.125047298538178</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.006941498792492215</v>
+        <v>-0.08671181820570938</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.03490749350466189</v>
+        <v>-0.1280370001694771</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>0</v>
@@ -7504,22 +7504,22 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.01727021521045463</v>
+        <v>-0.09397405179190549</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.002328720595975116</v>
+        <v>-0.004888917737341867</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04027734003277695</v>
+        <v>0.1512706223682102</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,19 +7531,19 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.002081474583438858</v>
+        <v>-0.1810945453073021</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.03559222545003354</v>
+        <v>0.3338938831516118</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01560792705641794</v>
+        <v>0.2844212768588201</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,25 +7552,25 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.007254371944179458</v>
+        <v>-0.0802391692736751</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.0001295470204526453</v>
+        <v>0.0009431892459991822</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02949784940910117</v>
+        <v>0.135166295674703</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7579,31 +7579,31 @@
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.01117673740080532</v>
+        <v>-0.05852024424311084</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02528574018344156</v>
+        <v>-0.08926250398908402</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0484975308667242</v>
+        <v>0.009686562757726405</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -7612,46 +7612,46 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.02040421186501677</v>
+        <v>0.005157954840920591</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.04173588385216163</v>
+        <v>0.09435067223928291</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.04615828815356267</v>
+        <v>0.1454902556228379</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01121710062763031</v>
+        <v>0.000341673244921276</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.001558830958664981</v>
+        <v>0.08989172513502773</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03835149906079329</v>
+        <v>0.1032285674534154</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7660,25 +7660,25 @@
         <v>-0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02269673278677555</v>
+        <v>-0.1094058618529177</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>5.427045335655309e-05</v>
+        <v>-0.033546066483209</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0.005742468238144342</v>
+        <v>0.02786316300742848</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7690,25 +7690,25 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01596346473514745</v>
+        <v>0.003823284919834274</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.03201502811501143</v>
+        <v>-0.04323982012784221</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.04633903457079024</v>
+        <v>0.1272968692592711</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7720,19 +7720,19 @@
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.01060471250556199</v>
+        <v>-0.1044561659879305</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.008014033653113498</v>
+        <v>-0.0285203928183922</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03167015458402955</v>
+        <v>0.1349573574185612</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
@@ -7741,52 +7741,52 @@
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.02473995106014412</v>
+        <v>-0.1517657204164483</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.006230463775177821</v>
+        <v>0.03584654138898938</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.03597341387602793</v>
+        <v>-0.0001165902941720828</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.001183397076480343</v>
+        <v>0.06055647502363189</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.04754886046772473</v>
+        <v>0.1813746267714983</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01225560912326404</v>
+        <v>-0.01147192105443562</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,34 +7795,34 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.01353666350497405</v>
+        <v>-0.06888123295758958</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01547506714617387</v>
+        <v>0.1017310339661465</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,16 +7830,16 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6492804134409371</v>
+        <v>0.2445804901053007</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2939539389067907</v>
+        <v>-0.133681369263182</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1194822813050385</v>
+        <v>-0.007422309158227642</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7851,22 +7851,22 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3607322487589307</v>
+        <v>0.2140564225595544</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.274510158929581</v>
+        <v>-0.177674584797792</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1203377065249719</v>
+        <v>-0.02498536939941495</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,82 +7881,82 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1366747692212969</v>
+        <v>0.03829614194265598</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.03411192252074274</v>
+        <v>-0.01442795383997047</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02170505397300855</v>
+        <v>-0.001949684851773447</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.09637772786254606</v>
+        <v>-0.07730354577521148</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.02888785567118826</v>
+        <v>-0.149035517492843</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.01158375459083028</v>
+        <v>-0.07673069805550085</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0003224971806198537</v>
+        <v>0.09084304358293088</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.06788683610543443</v>
+        <v>-0.05052216026789505</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.07370361835943866</v>
+        <v>0.04820865940193727</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -7965,73 +7965,73 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.5044902472627715</v>
+        <v>0.2151394424012294</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.01222238186413285</v>
+        <v>-0.007360451880784429</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.07422777139213108</v>
+        <v>-0.02396491734620609</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.05301455778367063</v>
+        <v>-0.005950275146097608</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.1660515658829282</v>
+        <v>-0.06456210603168459</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.250461407275876</v>
+        <v>-0.04858273634099711</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1518561376812254</v>
+        <v>0.03330340773838694</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04650287090341249</v>
+        <v>0.0194135872607302</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1943985006053761</v>
+        <v>0.1308414528540836</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -8046,46 +8046,46 @@
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.2510806988214314</v>
+        <v>0.2158852690109632</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.0008267654313361131</v>
+        <v>-0.02095772866613535</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.02036197076580663</v>
+        <v>0.02059233078516324</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1354341166043768</v>
+        <v>-0.08410428980311715</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02945295624560027</v>
+        <v>0.06933815782924474</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.02328345700774151</v>
+        <v>0.01811850363961233</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
         <v>-0</v>
@@ -8094,52 +8094,52 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.02001453470031643</v>
+        <v>-0.1322691946878261</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1424714907307637</v>
+        <v>0.1454755306383329</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1298067485414907</v>
+        <v>0.005977908753913375</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.1162799779007171</v>
+        <v>-0.07154145264166484</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.05759433995372666</v>
+        <v>0.07088490672702534</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01811902454858159</v>
+        <v>0.01987802595345037</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8148,31 +8148,31 @@
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.007505724781323288</v>
+        <v>0.002232792524028096</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.03886361853869076</v>
+        <v>-0.008491641832848553</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.02613593618304703</v>
+        <v>-0.04362918312513919</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
         <v>0</v>
@@ -8181,79 +8181,79 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.04910530825975112</v>
+        <v>-0.09338055791297022</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.05272542388511819</v>
+        <v>-0.03572576106964737</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.03873283964313835</v>
+        <v>0.03904088027609384</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.058641452725701</v>
+        <v>0.07441775219012352</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.004336596752264548</v>
+        <v>0.03011934534419373</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.03386978949650675</v>
+        <v>-0.06618320158722989</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.1107839462261372</v>
+        <v>-0.0110305303771284</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.06467284079671132</v>
+        <v>0.0600940844903142</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.06894363772468542</v>
+        <v>0.07337478240830236</v>
       </c>
       <c r="EK14" t="n">
         <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.09569921471144348</v>
+        <v>-0.05437851825888312</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.03345247744443874</v>
+        <v>0.06247630375843772</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02206196309949393</v>
+        <v>-0.02189853767350724</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,82 +8286,82 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.1215605260266948</v>
+        <v>-0.08694720658223472</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.037234917119999</v>
+        <v>0.07830699101480007</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.007469289341474064</v>
+        <v>0.0004290002752523863</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.01755243855232293</v>
+        <v>0.01546229103869289</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.07790089717722412</v>
+        <v>0.00646568530134244</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.05066833297266086</v>
+        <v>-0.09853781823090785</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.009092560515720832</v>
+        <v>-0.005603321416992618</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.02991402421600145</v>
+        <v>0.0266946479423849</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.02042347156147456</v>
+        <v>-0.03227752625335985</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
@@ -8370,19 +8370,19 @@
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.04360069368377027</v>
+        <v>-0.07555965976293627</v>
       </c>
       <c r="GA14" t="n">
         <v>-0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.07589982180819892</v>
+        <v>0.03456334310954266</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
@@ -8399,25 +8399,25 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.5896764627142477</v>
+        <v>-0.633845717861778</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.21239278567377</v>
+        <v>0.1912789133072613</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1484346689108451</v>
+        <v>0.1961944833608235</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
@@ -8426,43 +8426,43 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3985759898340645</v>
+        <v>-0.5025503419453641</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2364911851897736</v>
+        <v>0.3304445309080024</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05593971247813229</v>
+        <v>0.25535868970328</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1540955283323805</v>
+        <v>-0.07093706993534302</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.03809669391814002</v>
+        <v>0.08167008101147469</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.03100994926579306</v>
+        <v>-0.0568825252548548</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8477,55 +8477,55 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.2125351982801041</v>
+        <v>-0.04336273658762479</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.04817788364033308</v>
+        <v>0.2159970116646846</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.03298026066431381</v>
+        <v>0.01038010449899418</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.04772654417006592</v>
+        <v>-0.2198394320116087</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.03293472786190688</v>
+        <v>0.06567815650245086</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02252031580890516</v>
+        <v>-0.222553510462131</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
@@ -8534,19 +8534,19 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.3565697030887287</v>
+        <v>-0.5383207560980947</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.07026950313427655</v>
+        <v>0.1281777722006656</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.02268177262048425</v>
+        <v>0.03961161793199718</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -8561,16 +8561,16 @@
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.09824729160195705</v>
+        <v>0.05093465976637657</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1023780021489141</v>
+        <v>0.05677620448963189</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.3603028026955927</v>
+        <v>0.2729366367888975</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
@@ -8579,7 +8579,7 @@
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>-0</v>
@@ -8588,43 +8588,43 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.02993070382560619</v>
+        <v>0.08992578686575621</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.05454303940520999</v>
+        <v>0.02736874266722682</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1074964868799419</v>
+        <v>0.04247553913778962</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.2517594386222198</v>
+        <v>-0.4536678996353156</v>
       </c>
       <c r="BW15" t="n">
         <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.07901865440286622</v>
+        <v>0.120260655443913</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.04782045824149748</v>
+        <v>-0.02493466900770314</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,46 +8642,46 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1286009446599765</v>
+        <v>0.2833917450282699</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.03814880317354567</v>
+        <v>-0.05237116746251128</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.06994906973348211</v>
+        <v>-0.03374433601770704</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.05285869436722412</v>
+        <v>0.3268500672830791</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.01364225622787154</v>
+        <v>-0.0999163020847897</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.004438196870012514</v>
+        <v>-0.2884612314239117</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8696,70 +8696,70 @@
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.1346423848792344</v>
+        <v>0.2813378127228102</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.05371612474340474</v>
+        <v>-0.07567340960149578</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.04573323829693061</v>
+        <v>-0.04720749558499057</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1345189027431355</v>
+        <v>0.04397245319949237</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.03966070664493476</v>
+        <v>-0.008939582310236371</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.001365447817742847</v>
+        <v>-0.003613531033196055</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.1222972732601069</v>
+        <v>0.1704180490628207</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.09248871363283874</v>
+        <v>-0.01059323522619843</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1548823454895941</v>
+        <v>-0.0236911679454715</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8774,22 +8774,22 @@
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.05753362560860207</v>
+        <v>0.029507198759052</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.159390722877827</v>
+        <v>0.0131612859171784</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.1020567468652071</v>
+        <v>-0.06939972931182477</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8804,25 +8804,25 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.07941539048025455</v>
+        <v>0.2911916401066674</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.01584175747624807</v>
+        <v>-0.03147195733660874</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.06701938647723836</v>
+        <v>-0.01493926364707186</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
@@ -8831,70 +8831,70 @@
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.08632628363592267</v>
+        <v>0.2153129604749217</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.06966300367772769</v>
+        <v>-0.07706082371920565</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.07286728672392757</v>
+        <v>-0.1218062900290869</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1557819158262629</v>
+        <v>0.3384830888571586</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.06871987018935861</v>
+        <v>-0.05380024131449204</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03944022084450991</v>
+        <v>-0.03940168751017227</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.03953988308689829</v>
+        <v>0.1766987003236701</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.04664328430191348</v>
+        <v>-0.07270768607700792</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0227920536776248</v>
+        <v>0.02346635042842399</v>
       </c>
       <c r="FL15" t="n">
         <v>0</v>
@@ -8903,90 +8903,90 @@
         <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01924673752464403</v>
+        <v>0.02752731061781142</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.1311944202911667</v>
+        <v>-0.2097864593316096</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.03584026808854712</v>
+        <v>-0.01349170372461627</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0775443854031079</v>
+        <v>0.1510000369987023</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.1077614105399141</v>
+        <v>0.04652468622302128</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3345422045462771</v>
+        <v>0.2046570568045433</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1040163273759496</v>
+        <v>-0.1391635265088232</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05689265839859305</v>
+        <v>0.1642240210055048</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8998,22 +8998,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2614667340631677</v>
+        <v>0.1989677382213334</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1237982883111269</v>
+        <v>-0.1527060369184444</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1247101020966574</v>
+        <v>0.09332410777899654</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9025,19 +9025,19 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09688481565730274</v>
+        <v>0.03678761588890494</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.02582500224957221</v>
+        <v>-0.04709897140511093</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03479458580762092</v>
+        <v>-0.04232896098443257</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>-0</v>
@@ -9049,79 +9049,79 @@
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.06004206032099968</v>
+        <v>0.04169451288128199</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.03800396211726926</v>
+        <v>0.1198136114214554</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03052996765202319</v>
+        <v>0.0438756101125208</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.01928273281468286</v>
+        <v>0.04289646507611577</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.03078338412302969</v>
+        <v>-0.05927434488464093</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.06248062317465185</v>
+        <v>0.0002574403764750146</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.1529712139775669</v>
+        <v>0.1815730724655879</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.01858769403671884</v>
+        <v>-0.2317369779039581</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1708608151468087</v>
+        <v>-0.01095831038251931</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,16 +9130,16 @@
         <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0923004019583504</v>
+        <v>-0.001130502493756582</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.03984387068528213</v>
+        <v>0.1227698334268079</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.08900320377887121</v>
+        <v>0.07453582658333616</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -9154,49 +9154,49 @@
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.03816941572154151</v>
+        <v>-0.06788467592370474</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.05536851891374819</v>
+        <v>-0.07743821907492983</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1198218264601084</v>
+        <v>-0.1309883022584341</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.05954179341908349</v>
+        <v>0.1040804621528268</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0.02141594148381698</v>
+        <v>-0.1085156542285857</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.1117756655233817</v>
+        <v>-0.01275830279656665</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA16" t="n">
         <v>0</v>
@@ -9205,28 +9205,28 @@
         <v>-0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0.06959294209998884</v>
+        <v>-0.07832564682673127</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.02686093877623242</v>
+        <v>0.07135817575842671</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0004054989506993912</v>
+        <v>-0.04327651232711442</v>
       </c>
       <c r="CI16" t="n">
         <v>0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9235,19 +9235,19 @@
         <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.01418004503149746</v>
+        <v>-0.007151148316827923</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.003704657935527651</v>
+        <v>0.1652076682098198</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.1186674801633818</v>
+        <v>0.007519312428672886</v>
       </c>
       <c r="CR16" t="n">
         <v>0</v>
@@ -9256,34 +9256,34 @@
         <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
         <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0.05369284244981106</v>
+        <v>-0.05779338323976645</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.02648432469705512</v>
+        <v>0.06721353446840408</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.02319440181703224</v>
+        <v>-0.05769385527764437</v>
       </c>
       <c r="DA16" t="n">
         <v>-0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
         <v>0</v>
@@ -9292,16 +9292,16 @@
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0.03659946683637923</v>
+        <v>-0.01125307929713036</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.04330106983779596</v>
+        <v>0.02006291002408327</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.0056095734747765</v>
+        <v>-0.01911323884671937</v>
       </c>
       <c r="DJ16" t="n">
         <v>0</v>
@@ -9313,31 +9313,31 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
         <v>-0</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0.001868307312742693</v>
+        <v>-0.01811503225790511</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.02712015548731022</v>
+        <v>0.06966897874401506</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.1420395710614809</v>
+        <v>-0.06457514737998893</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
       </c>
       <c r="DT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,16 +9346,16 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.06473487613125521</v>
+        <v>0.02306792157768963</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0.002457176101492261</v>
+        <v>0.002836824704821441</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.05875099378788502</v>
+        <v>0.07843873381304853</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
@@ -9370,46 +9370,46 @@
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0.1110914001496662</v>
+        <v>-0.04259690716461582</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.04635818549333129</v>
+        <v>0.01440926960917821</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.05896696643402607</v>
+        <v>0.01298690560050956</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
         <v>0</v>
       </c>
       <c r="EQ16" t="n">
-        <v>-0.006860286306501331</v>
+        <v>-0.04952080273176031</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.030564743052281</v>
+        <v>0.07976747118282944</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02856841084114657</v>
+        <v>0.03088273895205181</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
@@ -9418,79 +9418,79 @@
         <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0.06724749697577918</v>
+        <v>-0.06279178689186302</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.04259430827403628</v>
+        <v>0.1039865954783983</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.02112461941074566</v>
+        <v>-0.04352554438357284</v>
       </c>
       <c r="FC16" t="n">
         <v>0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0.004725861477240727</v>
+        <v>-0.01953607261565314</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.005285212820973009</v>
+        <v>0.05611485805274248</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.07268587174485637</v>
+        <v>-0.03833534244464248</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0.004240599187395422</v>
+        <v>-0.0002425550803640829</v>
       </c>
       <c r="FS16" t="n">
-        <v>-0.007104763743604158</v>
+        <v>-0.009901281984594551</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.09031323925689508</v>
+        <v>0.2642630620146642</v>
       </c>
       <c r="FU16" t="n">
         <v>0</v>
@@ -9499,22 +9499,22 @@
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.04626409388790098</v>
+        <v>-0.02756181751235361</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.05480273634979909</v>
+        <v>0.147349977541285</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
@@ -9537,19 +9537,19 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.185761519164108</v>
+        <v>0.2373337824054026</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08280529374313922</v>
+        <v>-0.04664687109060651</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05906482528137331</v>
+        <v>-0.1340200125569248</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
@@ -9564,34 +9564,34 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1296497095568202</v>
+        <v>0.3315054476781985</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05609002565123491</v>
+        <v>-0.1098442723696418</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.03579135002131095</v>
+        <v>-0.08628771016387786</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01864672818254303</v>
+        <v>0.04872839620026031</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
@@ -9600,40 +9600,40 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.02887223281028661</v>
+        <v>-0.03340991195670458</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02786397998979286</v>
+        <v>0.008096385628725463</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
         <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0305368007271461</v>
+        <v>-0.01956221671455853</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.02202576027203309</v>
+        <v>-0.1385505748666266</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.003733405023159691</v>
+        <v>0.01043333309798664</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9642,25 +9642,25 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.02968125502208196</v>
+        <v>0.04047913756227129</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01786262120572332</v>
+        <v>-0.03809372585761372</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.02616291587461859</v>
+        <v>-0.02875975100417511</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,118 +9669,118 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1149478478685116</v>
+        <v>0.2745906257057886</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.0609388444850836</v>
+        <v>-0.1416871081255964</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.04359743020474337</v>
+        <v>-0.1303191517975555</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04113471601615659</v>
+        <v>0.008643997258531584</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.033586889642026</v>
+        <v>-0.06500036801438434</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.008106854990944429</v>
+        <v>-0.02634758994888761</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.05040382219578231</v>
+        <v>0.05444417493742189</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.02459522723025488</v>
+        <v>0.06717108733144284</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.01557470893925633</v>
+        <v>0.03110582372546847</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.06765178711632917</v>
+        <v>0.162188570237383</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.03238911692027842</v>
+        <v>-0.04971851313415511</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.01062193215397759</v>
+        <v>-0.04817218318348154</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD17" t="n">
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.02639414156272516</v>
+        <v>-0.06009311427689332</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -9789,10 +9789,10 @@
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.008559142952868666</v>
+        <v>0.04657745749659409</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.01613051095244695</v>
+        <v>0.0473388649676917</v>
       </c>
       <c r="CJ17" t="n">
         <v>-0</v>
@@ -9801,25 +9801,25 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.001681295693012171</v>
+        <v>-0.1402564251143357</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.01275195504509536</v>
+        <v>0.1663840163365967</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.02093154650694527</v>
+        <v>0.02888167853639684</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9828,25 +9828,25 @@
         <v>-0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.01952888184489697</v>
+        <v>-0.05969681219856627</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.004553180121479291</v>
+        <v>0.02477936644056983</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.02295379872539117</v>
+        <v>0.05340759886381242</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9861,76 +9861,76 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.009446839789090784</v>
+        <v>-0.02083197696270756</v>
       </c>
       <c r="DG17" t="n">
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.008389746392797848</v>
+        <v>-0.009575962464975501</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.004198287361923691</v>
+        <v>0.01331555364932408</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.02386988757301259</v>
+        <v>-0.04542119480032425</v>
       </c>
       <c r="DP17" t="n">
         <v>0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.02125622512683335</v>
+        <v>0.02420069833244502</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.02144786251296666</v>
+        <v>0.05889706618060261</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.005336672732941069</v>
+        <v>0.009052221199594909</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.02320332016238783</v>
+        <v>-0.03972497463145754</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.01488335116879579</v>
+        <v>0.02351453101027287</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,64 +9939,64 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.01621237883264771</v>
+        <v>-0.01691858519304042</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01577216402764448</v>
+        <v>-0.01511575908304665</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.007292625230345929</v>
+        <v>0.04132552207182115</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.0006805769808963989</v>
+        <v>-0.01247909489221269</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.0091960118702764</v>
+        <v>-0.0351153914092676</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.02677545493915625</v>
+        <v>-0.04888710252002696</v>
       </c>
       <c r="EU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW17" t="n">
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.01688998410672381</v>
+        <v>-0.06777234964664682</v>
       </c>
       <c r="EZ17" t="n">
         <v>0</v>
@@ -10005,13 +10005,13 @@
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.001741843322154773</v>
+        <v>0.02912177892940906</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0234164705170184</v>
+        <v>0.04570943807231771</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10023,7 +10023,7 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.02039740211811467</v>
+        <v>-0.05752168489926519</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
@@ -10032,25 +10032,25 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.03842939906323027</v>
+        <v>0.05886615091126102</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01951696093881562</v>
+        <v>-0.02431818055466254</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.002203766585031614</v>
+        <v>-0.004117442018878573</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,43 +10059,43 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.001105556594987681</v>
+        <v>0.003514809466212202</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01600898399904726</v>
+        <v>-0.01279937676912598</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.02248658517898526</v>
+        <v>-0.0420893872409336</v>
       </c>
       <c r="GA17" t="n">
         <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.02490499780259479</v>
+        <v>0.02395882063395312</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
